--- a/output/pdf_financials_xlsx/FTG.xlsx
+++ b/output/pdf_financials_xlsx/FTG.xlsx
@@ -895,43 +895,43 @@
         <v>14.265</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8.253</v>
+        <v>11.512</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8.259</v>
+        <v>11.669</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8.747</v>
+        <v>13.375</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9.43</v>
+        <v>12.74</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10.018</v>
+        <v>7.453</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>11.259</v>
+        <v>11.779</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>12.508</v>
+        <v>19.628</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>13.333</v>
+        <v>18.982</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>13.732</v>
+        <v>20.536</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>10.95</v>
+        <v>14.555</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.678</v>
+        <v>18.968</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>16.961</v>
+        <v>25.235</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.02035</v>
+        <v>29.003</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0.026683</v>
@@ -950,43 +950,43 @@
         <v>-1.278</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.027</v>
+        <v>0.768</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4.369</v>
+        <v>0.959</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.649</v>
+        <v>-1.979</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5.756</v>
+        <v>2.446</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8.016</v>
+        <v>10.581</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>8.093999999999999</v>
+        <v>7.574</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>10.617</v>
+        <v>3.497</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.929</v>
+        <v>6.28</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>16.532</v>
+        <v>9.728</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.183</v>
+        <v>2.578</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>8.632</v>
+        <v>2.342</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>22.324</v>
+        <v>14.05</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.023826</v>
+        <v>-28.958824</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0.033849</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.026</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>7.647</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>20.196</v>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.026</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>7.647</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>20.196</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.184</v>
+        <v>1.014</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.439</v>
+        <v>1.419</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>7.676</v>
+        <v>2.65</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>9.849</v>
+        <v>2.202</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>3.981</v>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -18554,7 +18554,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -46960,7 +46960,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -53026,7 +53026,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">

--- a/output/pdf_financials_xlsx/FTG.xlsx
+++ b/output/pdf_financials_xlsx/FTG.xlsx
@@ -2032,10 +2032,10 @@
         <v>0.048</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.049</v>
+        <v>0.168</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.049</v>
+        <v>0.156</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.479</v>
@@ -2050,19 +2050,19 @@
         <v>1.128</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.24</v>
+        <v>6.289</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.124</v>
+        <v>5.733</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.193</v>
+        <v>7.011</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.203285</v>
+        <v>0.000195</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.009454000000000001</v>
+        <v>0.001242</v>
       </c>
     </row>
     <row r="29">
@@ -2087,10 +2087,10 @@
         <v>-1.931</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.495</v>
+        <v>2.614</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10.63</v>
+        <v>10.737</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>8.053000000000001</v>
@@ -2105,19 +2105,19 @@
         <v>10.856</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.818</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.466</v>
+        <v>8.074999999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>14.243</v>
+        <v>21.061</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.218458</v>
+        <v>0.015368</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.027911</v>
+        <v>0.019699</v>
       </c>
     </row>
     <row r="30">
@@ -2142,10 +2142,10 @@
         <v>-3.448337440622879</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.110446630092753</v>
+        <v>4.306495988401786</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>14.75466722187522</v>
+        <v>14.90318550905684</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>9.244208737975526</v>
@@ -2160,19 +2160,19 @@
         <v>9.636671903988352</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>3.550683550683551</v>
+        <v>11.17243117243117</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>2.751495135231635</v>
+        <v>9.009863429438543</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>10.53476331360947</v>
+        <v>15.57766272189349</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>134.7707531339453</v>
+        <v>9.480801500345475</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>14.61339504492241</v>
+        <v>10.3138285618547</v>
       </c>
     </row>
     <row r="31">
@@ -6821,49 +6821,49 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.479</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.107</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.049</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.128</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>6.289</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>5.733</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>7.011</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>8.48</v>
       </c>
       <c r="Q100" s="3" t="n">
         <v>0</v>
@@ -7487,13 +7487,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7505,13 +7505,13 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -24118,7 +24118,11 @@
           <t>Depreciation of property, plant and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -24210,7 +24214,11 @@
           <t>Depreciation of right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -24304,7 +24312,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -27816,7 +27824,11 @@
           <t>Depreciation of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -27910,7 +27922,11 @@
           <t>Depreciation of right-of-use assets (Note 8)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -28006,7 +28022,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -29600,7 +29616,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -30522,7 +30538,11 @@
           <t>Proceeds from disposal of plant and equipment</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -34632,7 +34652,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -36334,7 +36354,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
@@ -42184,7 +42204,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -45656,7 +45676,11 @@
           <t>Depreciation of property, plant and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -45748,7 +45772,11 @@
           <t>Depreciation of right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -46022,7 +46050,11 @@
           <t>Depreciation of property, plant and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -46114,7 +46146,11 @@
           <t>Depreciation of right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -46208,7 +46244,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -47962,7 +47998,11 @@
           <t>Depreciation of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -48056,7 +48096,11 @@
           <t>Depreciation of right-of-use assets (Note 8)</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -48338,7 +48382,11 @@
           <t>Depreciation of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -48432,7 +48480,11 @@
           <t>Depreciation of right-of-use assets (Note 8)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -48528,7 +48580,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -50380,7 +50432,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -52352,7 +52404,11 @@
           <t>Depreciation of plant and equipment and amortization of intangible assets (Note 8, Note 9)</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -54190,7 +54246,11 @@
           <t>Depreciation of plant and equipment, amortization of intangible assets (Note 7, Note 8)</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -59656,7 +59716,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E540" s="5" t="n">

--- a/output/pdf_financials_xlsx/FTG.xlsx
+++ b/output/pdf_financials_xlsx/FTG.xlsx
@@ -1515,7 +1515,7 @@
         <v>0.928</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.969</v>
+        <v>-1.038</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>2.158</v>
@@ -1680,7 +1680,7 @@
         <v>0.928</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.969</v>
+        <v>-1.038</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>2.158</v>
@@ -2249,7 +2249,7 @@
         <v>1.667685008805665</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-1.730418943533698</v>
+        <v>-1.853637629915354</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>3.555248027150365</v>
@@ -6778,7 +6778,7 @@
         <v>0.928</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.969</v>
+        <v>-1.038</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>2.158</v>
@@ -7151,52 +7151,52 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-2.733</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>2.538</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>1.974</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-1.629</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-1.025</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-1.003</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.453</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-14.672</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-2.053</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>3.869</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>3.192</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>3.457</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-7.656</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-0.006472</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-0.009124</v>
       </c>
     </row>
     <row r="107">
@@ -21530,7 +21530,11 @@
           <t>Net change in non-cash operating working capital 15</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -24872,7 +24876,11 @@
           <t>Net change in non-cash operating working capital (Note 15)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -28502,7 +28510,11 @@
           <t>Net change in non-cash operating working capital (Note 14)</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -30068,7 +30080,11 @@
           <t>Net change in non-cash operating working capital (Note 16)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -31558,7 +31574,11 @@
           <t>Net change in non-cash operating working capital(Note 16)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -32580,7 +32600,11 @@
           <t>Deferred income tax expense (Note 15.1 and Note 15.2)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -32766,7 +32790,11 @@
           <t>Net change in non-cash operating working capital (Note 16)</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -34748,7 +34776,11 @@
           <t>Deferred income tax expense (Note 14.1 and Note 14.2)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -35316,7 +35348,11 @@
           <t>Net change in non-cash operating working capital (Note 15)</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -36632,7 +36668,11 @@
           <t>Deferred income tax expense (recovery) (Note 15.2)</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -36726,7 +36766,11 @@
           <t>Net change in non-cash operating working capital (Note 16)</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -37872,7 +37916,11 @@
           <t>Deferred income tax recovery (Note 16.2)</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -38156,7 +38204,11 @@
           <t>Changes in non-cash operating working capital (Note 17)</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -39292,7 +39344,11 @@
           <t>Changes in non-cash operating working capital (Note 18)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -39770,7 +39826,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E329" s="5" t="n">
         <v>-0.173</v>
       </c>
@@ -39960,7 +40020,11 @@
           <t>Changes in non-cash operating working capital (Note 14)</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E331" s="5" t="n">
         <v>-2.733</v>
       </c>
@@ -47806,7 +47870,11 @@
           <t>Deferred income tax recovery (Note 14.1)</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -49442,7 +49510,11 @@
           <t>Deferred income tax recovery (Note 13.1)</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -50900,7 +50972,11 @@
           <t>Deferred income tax (recovery) expense (Note 15.1, Note 15.2)</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -56164,7 +56240,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -56936,7 +57016,11 @@
           <t>Deferred income tax recovery (Note 16.2)</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
